--- a/evaluation/det_gpt_realset.xlsx
+++ b/evaluation/det_gpt_realset.xlsx
@@ -349,7 +349,7 @@
         <v>1.0</v>
       </c>
       <c r="D1" s="0" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="2">
@@ -365,7 +365,7 @@
         <v>0.7150400589194947</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>0.4766666666666667</v>
+        <v>0.7383333333333333</v>
       </c>
     </row>
     <row r="3">
@@ -381,7 +381,7 @@
         <v>0.2777777777777778</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>0.09444444444444444</v>
+        <v>0.4996031746031746</v>
       </c>
     </row>
     <row r="4">
@@ -397,7 +397,7 @@
         <v>0.20927462217480713</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>0.075</v>
+        <v>0.3859848484848485</v>
       </c>
     </row>
     <row r="5">
@@ -409,15 +409,11 @@
       <c r="B5" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="0" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="D5" s="0" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
+      <c r="C5" s="0" t="n">
+        <v>0.5862778317723522</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>0.29049625468164797</v>
       </c>
     </row>
     <row r="6">
@@ -449,7 +445,7 @@
         <v>0.4434377333227159</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>0.44696969696969696</v>
+        <v>0.6800065876152833</v>
       </c>
     </row>
     <row r="8">
@@ -465,7 +461,7 @@
         <v>0.624401890421459</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>0.6372377622377623</v>
+        <v>0.7582740535326742</v>
       </c>
     </row>
     <row r="9">
@@ -481,7 +477,7 @@
         <v>0.375</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>0.4300899621212122</v>
+        <v>0.6525449810606061</v>
       </c>
     </row>
     <row r="10">
@@ -497,7 +493,7 @@
         <v>0.4444444444444444</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>0.4904761904761905</v>
+        <v>0.7011204481792717</v>
       </c>
     </row>
     <row r="11">
@@ -545,7 +541,7 @@
         <v>0.362027253439254</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>0.2569444444444444</v>
+        <v>0.6046626984126984</v>
       </c>
     </row>
     <row r="14">
@@ -561,7 +557,7 @@
         <v>0.45662131993964766</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>0.15833333333333335</v>
+        <v>0.5599358974358974</v>
       </c>
     </row>
     <row r="15">
@@ -577,7 +573,7 @@
         <v>0.25</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>0.06998275162337662</v>
+        <v>0.4490538758116883</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +589,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>0.09294871794871797</v>
+        <v>0.45951783723522854</v>
       </c>
     </row>
     <row r="17">
@@ -609,7 +605,7 @@
         <v>0.5333333333333333</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>0.4675324675324675</v>
+        <v>0.7018513401492125</v>
       </c>
     </row>
     <row r="18">
@@ -625,7 +621,7 @@
         <v>0.8054984382550932</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>0.45708333333333345</v>
+        <v>0.7216923515981736</v>
       </c>
     </row>
     <row r="19">
@@ -657,7 +653,7 @@
         <v>0.4</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>0.16301020408163266</v>
+        <v>0.5030737294917967</v>
       </c>
     </row>
     <row r="21">
@@ -673,7 +669,7 @@
         <v>0.25</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5897435897435898</v>
       </c>
     </row>
     <row r="22">
@@ -689,7 +685,7 @@
         <v>0.36705766336943857</v>
       </c>
       <c r="D22" s="0" t="n">
-        <v>0.4236111111111111</v>
+        <v>0.6909722222222222</v>
       </c>
     </row>
   </sheetData>

--- a/evaluation/det_gpt_realset.xlsx
+++ b/evaluation/det_gpt_realset.xlsx
@@ -333,7 +333,7 @@
     <col width="17.6" min="1" max="1" bestFit="1" customWidth="1"/>
     <col width="5.5" min="2" max="2" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="3" max="3" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="4" max="4" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="4" max="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -349,7 +349,7 @@
         <v>1.0</v>
       </c>
       <c r="D1" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666667</v>
       </c>
     </row>
     <row r="2">
@@ -365,7 +365,7 @@
         <v>0.7150400589194947</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>0.7383333333333333</v>
+        <v>0.4766666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -381,7 +381,7 @@
         <v>0.2777777777777778</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>0.4996031746031746</v>
+        <v>0.08544973544973544</v>
       </c>
     </row>
     <row r="4">
@@ -397,7 +397,7 @@
         <v>0.20927462217480713</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>0.3859848484848485</v>
+        <v>0.052272727272727276</v>
       </c>
     </row>
     <row r="5">
@@ -413,7 +413,7 @@
         <v>0.5862778317723522</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>0.29049625468164797</v>
+        <v>0.01413164100430018</v>
       </c>
     </row>
     <row r="6">
@@ -445,7 +445,7 @@
         <v>0.4434377333227159</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>0.6800065876152833</v>
+        <v>0.408102766798419</v>
       </c>
     </row>
     <row r="8">
@@ -461,7 +461,7 @@
         <v>0.624401890421459</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>0.7582740535326742</v>
+        <v>0.5603297564504461</v>
       </c>
     </row>
     <row r="9">
@@ -477,7 +477,7 @@
         <v>0.375</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>0.6525449810606061</v>
+        <v>0.3763287168560607</v>
       </c>
     </row>
     <row r="10">
@@ -493,7 +493,7 @@
         <v>0.4444444444444444</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>0.7011204481792717</v>
+        <v>0.44719887955182075</v>
       </c>
     </row>
     <row r="11">
@@ -541,7 +541,7 @@
         <v>0.362027253439254</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>0.6046626984126984</v>
+        <v>0.24470899470899468</v>
       </c>
     </row>
     <row r="14">
@@ -557,7 +557,7 @@
         <v>0.45662131993964766</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>0.5599358974358974</v>
+        <v>0.15224358974358976</v>
       </c>
     </row>
     <row r="15">
@@ -573,7 +573,7 @@
         <v>0.25</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>0.4490538758116883</v>
+        <v>0.05795446618810877</v>
       </c>
     </row>
     <row r="16">
@@ -589,7 +589,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>0.45951783723522854</v>
+        <v>0.07678372352285397</v>
       </c>
     </row>
     <row r="17">
@@ -605,7 +605,7 @@
         <v>0.5333333333333333</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>0.7018513401492125</v>
+        <v>0.4376899696048632</v>
       </c>
     </row>
     <row r="18">
@@ -621,7 +621,7 @@
         <v>0.8054984382550932</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>0.7216923515981736</v>
+        <v>0.4508219178082193</v>
       </c>
     </row>
     <row r="19">
@@ -653,7 +653,7 @@
         <v>0.4</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>0.5030737294917967</v>
+        <v>0.13743997599039617</v>
       </c>
     </row>
     <row r="21">
@@ -669,7 +669,7 @@
         <v>0.25</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>0.5897435897435898</v>
+        <v>0.28205128205128205</v>
       </c>
     </row>
     <row r="22">
@@ -685,7 +685,7 @@
         <v>0.36705766336943857</v>
       </c>
       <c r="D22" s="0" t="n">
-        <v>0.6909722222222222</v>
+        <v>0.40596064814814814</v>
       </c>
     </row>
   </sheetData>
